--- a/Assets/Resources/EquipItemDataBase.xlsx
+++ b/Assets/Resources/EquipItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\SangDol\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5626664-4824-41AE-9E60-84799145300C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F67ADAC2-276B-4CD2-8D36-E265E7D0D88E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3360" yWindow="7395" windowWidth="19845" windowHeight="11295" xr2:uid="{376D98C0-2A4B-47A6-A4D5-BC2FDC188FE2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6EAF4D32-D501-4D72-AA72-8C2EEF7028C9}"/>
   </bookViews>
   <sheets>
     <sheet name="EquipItemDataBase" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="52">
   <si>
     <t>ID</t>
   </si>
@@ -40,6 +40,9 @@
     <t>Desc</t>
   </si>
   <si>
+    <t>Price</t>
+  </si>
+  <si>
     <t>EquipType</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>Value</t>
   </si>
   <si>
+    <t>CanUpgrade</t>
+  </si>
+  <si>
     <t>TestHead</t>
   </si>
   <si>
@@ -73,9 +79,6 @@
     <t>테스트용 장비 상의</t>
   </si>
   <si>
-    <t>Uncommon</t>
-  </si>
-  <si>
     <t>Body</t>
   </si>
   <si>
@@ -88,9 +91,6 @@
     <t>테스트용 장비 장갑</t>
   </si>
   <si>
-    <t>Rare</t>
-  </si>
-  <si>
     <t>Gloves</t>
   </si>
   <si>
@@ -103,43 +103,80 @@
     <t>테스트용 장비 하의</t>
   </si>
   <si>
+    <t>Pants</t>
+  </si>
+  <si>
+    <t>MoveSpeed</t>
+  </si>
+  <si>
+    <t>TestShoes</t>
+  </si>
+  <si>
+    <t>테스트용 장비 신발</t>
+  </si>
+  <si>
+    <t>Shoes</t>
+  </si>
+  <si>
+    <t>AttackSpeed</t>
+  </si>
+  <si>
+    <t>TestWeapon</t>
+  </si>
+  <si>
+    <t>테스트용 장비 무기</t>
+  </si>
+  <si>
+    <t>Weapon</t>
+  </si>
+  <si>
+    <t>CriticalChance</t>
+  </si>
+  <si>
+    <t>Wolf_Head</t>
+  </si>
+  <si>
+    <t>늑대왕의 투구</t>
+  </si>
+  <si>
     <t>Unique</t>
   </si>
   <si>
-    <t>Pants</t>
-  </si>
-  <si>
-    <t>MoveSpeed</t>
-  </si>
-  <si>
-    <t>TestShoes</t>
-  </si>
-  <si>
-    <t>테스트용 장비 신발</t>
-  </si>
-  <si>
-    <t>Legendary</t>
-  </si>
-  <si>
-    <t>Shoes</t>
-  </si>
-  <si>
-    <t>AttackSpeed</t>
-  </si>
-  <si>
-    <t>TestWeapon</t>
-  </si>
-  <si>
-    <t>테스트용 장비 무기</t>
-  </si>
-  <si>
-    <t>Weapon</t>
-  </si>
-  <si>
-    <t>CriticalChance</t>
-  </si>
-  <si>
-    <t>Price</t>
+    <t>Wolf_Body</t>
+  </si>
+  <si>
+    <t>늑대왕의 갑옷</t>
+  </si>
+  <si>
+    <t>Wolf_Gloves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">늑대왕의 </t>
+  </si>
+  <si>
+    <t>Wolf_Pants</t>
+  </si>
+  <si>
+    <t>늑대왕의 레깅스</t>
+  </si>
+  <si>
+    <t>Wolf_Shoes</t>
+  </si>
+  <si>
+    <t>늑대왕의 신발</t>
+  </si>
+  <si>
+    <t>Wolf_Weapon</t>
+  </si>
+  <si>
+    <t>늑대왕의 건틀렛</t>
+  </si>
+  <si>
+    <t>MaxUpgrade</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>BonusValue</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1111,23 +1148,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78226173-4436-4D0C-A21F-70D1DF4135D0}">
-  <dimension ref="A1:K7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{793AE615-3163-4772-B79C-25F8F8E1C526}">
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6.375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1147,48 +1188,57 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N1" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>10001</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D2">
         <v>10001</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G2">
         <v>100</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -1196,34 +1246,43 @@
       <c r="K2">
         <v>10</v>
       </c>
+      <c r="L2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>99</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>10002</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D3">
         <v>10002</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G3">
         <v>110</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -1231,25 +1290,34 @@
       <c r="K3">
         <v>0.5</v>
       </c>
+      <c r="L3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>99</v>
+      </c>
+      <c r="N3">
+        <v>0.01</v>
+      </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>10003</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4">
         <v>10003</v>
       </c>
       <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
         <v>22</v>
-      </c>
-      <c r="F4" t="s">
-        <v>21</v>
       </c>
       <c r="G4">
         <v>120</v>
@@ -1266,8 +1334,17 @@
       <c r="K4">
         <v>10</v>
       </c>
+      <c r="L4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>99</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>10004</v>
       </c>
@@ -1281,7 +1358,7 @@
         <v>10004</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
         <v>26</v>
@@ -1290,10 +1367,10 @@
         <v>130</v>
       </c>
       <c r="H5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" t="s">
         <v>28</v>
-      </c>
-      <c r="I5" t="s">
-        <v>29</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1301,34 +1378,43 @@
       <c r="K5">
         <v>0.2</v>
       </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>99</v>
+      </c>
+      <c r="N5">
+        <v>0.01</v>
+      </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>10005</v>
       </c>
       <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
         <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
       </c>
       <c r="D6">
         <v>10005</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G6">
         <v>140</v>
       </c>
       <c r="H6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1336,40 +1422,322 @@
       <c r="K6">
         <v>0.3</v>
       </c>
+      <c r="L6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>99</v>
+      </c>
+      <c r="N6">
+        <v>0.01</v>
+      </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>10006</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D7">
         <v>10006</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G7">
         <v>150</v>
       </c>
       <c r="H7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7">
         <v>0.5</v>
+      </c>
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>99</v>
+      </c>
+      <c r="N7">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>10007</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8">
+        <v>10007</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>50</v>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>5</v>
+      </c>
+      <c r="N8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>10008</v>
+      </c>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9">
+        <v>10008</v>
+      </c>
+      <c r="E9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>50</v>
+      </c>
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>5</v>
+      </c>
+      <c r="N9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>10009</v>
+      </c>
+      <c r="B10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10">
+        <v>10009</v>
+      </c>
+      <c r="E10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>0.1</v>
+      </c>
+      <c r="L10" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>5</v>
+      </c>
+      <c r="N10">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10010</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11">
+        <v>10010</v>
+      </c>
+      <c r="E11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>50</v>
+      </c>
+      <c r="L11" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>5</v>
+      </c>
+      <c r="N11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>10011</v>
+      </c>
+      <c r="B12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12">
+        <v>10011</v>
+      </c>
+      <c r="E12" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0.1</v>
+      </c>
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>5</v>
+      </c>
+      <c r="N12">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>10012</v>
+      </c>
+      <c r="B13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13">
+        <v>10012</v>
+      </c>
+      <c r="E13" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>50</v>
+      </c>
+      <c r="L13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>5</v>
+      </c>
+      <c r="N13">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
